--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/09_体制届チェックシート.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/09_体制届チェックシート.xlsx
@@ -518,12 +518,12 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>処遇改善加算（Ⅰ）</t>
+          <t>福祉・介護職員等処遇改善加算（Ⅰ）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>基本報酬×約15-20%</t>
+          <t>基本報酬×サービス別加算率</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>計画書提出・職場環境整備確認</t>
+          <t>計画書提出・職場環境整備確認（旧3加算は一本化）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -579,14 +579,14 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>月6,400円</t>
+          <t>ロ6,520円/イ6,800円（月）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>24時間連絡・緊急訪問体制整備</t>
+          <t>24時間連絡・緊急訪問体制整備（イは負担軽減の取組2項目以上）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">

--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/09_体制届チェックシート.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/09_体制届チェックシート.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="体制届チェックシート" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="体制届チェック" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,29 +26,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFDC2626"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <i val="1"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +63,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="00F6EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9854A"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -70,28 +81,68 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,222 +507,295 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>体制届チェックシート（加算算定管理用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>体制届チェックシート</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【重要】体制届を出さずに加算を算定すると不正請求となります。算定開始月の前月末日までに届出が必要です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t>加算の体制届は算定開始月の前月末日までに提出。未提出での算定は不正請求となる</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>【重要】体制等状況一覧表＋各加算の届出書を、国保連・支払基金（医療）／市町村・京都府（障害福祉）へ前月末までに提出。</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>加算名</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>単位数</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>届出提出日</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>算定額/単位（参考）</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>届出日</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>算定開始月</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>要件充足確認</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>次回更新・注意事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>要件充足の確認</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>次回更新・注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>福祉・介護職員等処遇改善加算（Ⅰ）</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>基本報酬×サービス別加算率</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>毎年4/15</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>毎年6月〜</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>計画書提出・職場環境整備確認（旧3加算は一本化）</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>毎年更新（7/31実績報告）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>基本報酬×サービス別率</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>計画書提出・職場環境整備（旧3加算は一本化）</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>毎年4/15計画・7/31実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>24時間対応体制加算（訪問看護）</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ロ6,520円／イ6,800円（月）</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>24時間連絡・緊急訪問体制（イは負担軽減2項目以上）</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>体制変更時に届出</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>特別管理加算（訪問看護）</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Ⅰ5,000円／Ⅱ2,500円（月）</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>対象疾患・医療処置の確認</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>目標工賃達成加算（B型）</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>10単位/日</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>前年度平均工賃が目標以上</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>毎年度確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>福祉専門職員配置等加算（Ⅰ）</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>15単位/日</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>有資格者比率25%以上を確認</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>有資格者比率25%以上</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>職員変更時に再確認</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>24時間対応体制加算</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ロ6,520円/イ6,800円（月）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>24時間連絡・緊急訪問体制整備（イは負担軽減の取組2項目以上）</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>体制変更時に届出変更必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>目標工賃達成加算（B型）</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>10単位/日</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>前年度平均工賃が目標値以上</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>毎年度確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>強度行動障害支援者配置加算</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>7〜42単位/日</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>研修修了者の配置確認</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>職員変更時に再確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>精神障害者支援体制加算</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>7〜28単位/日</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>研修修了者の配置確認</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>職員変更時に再確認</t>
-        </is>
-      </c>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>就労移行支援体制加算</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>27〜100単位/日等</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>前年度の一般就労実績</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>毎年4月届出</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>※ 金額・単位は令和6年度（2024年度）改定後の参考値。令和8年度（2026年6月）改定後の値は最新告示で確認。</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>